--- a/test_rooms.xlsx
+++ b/test_rooms.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -481,13 +481,43 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>CR-104</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>60</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>LAB-201</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B6" t="n">
         <v>30</v>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>LAB-202</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>30</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lab</t>
         </is>

--- a/test_rooms.xlsx
+++ b/test_rooms.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="rooms" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -496,28 +496,118 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>LAB-201</t>
+          <t>CR-105</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>classroom</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>CR-106</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>60</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>CR-107</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>60</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>CR-108</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>60</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>LAB-201</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>LAB-202</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>30</v>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>LAB-203</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>40</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lab</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LAB-204</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>40</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>lab</t>
         </is>
